--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260805.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.23%</t>
+          <t>11.32%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.65%</t>
+          <t>10.67%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>35,455</t>
+          <t>90,125</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.95%</t>
+          <t>8.13%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>90,125</t>
+          <t>35,455</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.86%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.72%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1034,117 +1034,117 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>51,110</t>
+          <t>46,927</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>46,927</t>
+          <t>32,410</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>32,410</t>
+          <t>51,110</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>94,763</t>
+          <t>30,345</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,345</t>
+          <t>94,763</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1188,73 +1188,73 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>27,469</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>27,469</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1474,24 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1628,51 +1628,51 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>8,021</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,021</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>104,749,756</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
